--- a/WorkBot/main/data/order_archive/Webstaurant/Webstaurant_Bakery_20260726.xlsx
+++ b/WorkBot/main/data/order_archive/Webstaurant/Webstaurant_Bakery_20260726.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,6 +563,111 @@
         <v>326.99</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10207579</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Salt - Sea Coarse</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23.37</v>
+      </c>
+      <c r="E10" t="n">
+        <v>46.74</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>477102016</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Doilies - Lace (16")</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>36.17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2458GCC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cake Circle - 8" (Gold)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="E12" t="n">
+        <v>80.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>245CCGR1410BL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/4 Sheet</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="E13" t="n">
+        <v>85.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>245CCGR1914</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cake Board - 1/2 Sheet</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>42.59</v>
+      </c>
+      <c r="E14" t="n">
+        <v>127.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
